--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486282_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486282_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3688</v>
+        <v>-0.9654</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0586</v>
+        <v>-1.3313</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4275</v>
+        <v>0.3658</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7292</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7591</v>
+        <v>0.4248</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7557</v>
+        <v>0.4831</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0034</v>
+        <v>-0.0583</v>
       </c>
       <c r="V2" t="n">
         <v>-0.226</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.5431</v>
+        <v>-1.1571</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7282999999999999</v>
+        <v>0.3043</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8148</v>
+        <v>-1.4614</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6601</v>
+        <v>-2.5402</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5542</v>
+        <v>-0.1401</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8941</v>
+        <v>-2.4001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6222</v>
+        <v>-0.822</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1428</v>
+        <v>0.8577</v>
       </c>
       <c r="L3" t="n">
-        <v>0.765</v>
+        <v>-1.6797</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2823</v>
+        <v>-1.7182</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4114</v>
+        <v>-0.9978</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1291</v>
+        <v>-0.7204</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.161</v>
+        <v>-0.5861</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1286</v>
+        <v>-0.3941</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0324</v>
+        <v>-0.192</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.479</v>
+        <v>1.0992</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.479</v>
+        <v>1.5204</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.4212</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.6671</v>
+        <v>-1.8784</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2365</v>
+        <v>-1.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4306</v>
+        <v>-0.8148</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5402</v>
+        <v>-0.6601</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1401</v>
+        <v>-1.5542</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4001</v>
+        <v>0.8941</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.822</v>
+        <v>0.6222</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8577</v>
+        <v>-0.1428</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.6797</v>
+        <v>0.765</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7182</v>
+        <v>-1.2823</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9978</v>
+        <v>-1.4114</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7204</v>
+        <v>0.1291</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0961</v>
+        <v>-0.1742</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9349</v>
+        <v>-0.2067</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1612</v>
+        <v>0.0324</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0992</v>
+        <v>-1.479</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5204</v>
+        <v>-1.479</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.0665</v>
+        <v>-2.575</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.8968</v>
+        <v>-2.3128</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1697</v>
+        <v>-0.2621</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0268</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7262</v>
+        <v>-0.2346</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9589</v>
+        <v>-0.3749</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2328</v>
+        <v>0.1403</v>
       </c>
       <c r="V5" t="n">
         <v>-0.226</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.8148</v>
+        <v>-5.0691</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3614</v>
+        <v>-0.3429</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.4533</v>
+        <v>-4.7262</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.3077</v>
+        <v>-1.2475</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2566</v>
+        <v>-1.4507</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0511</v>
+        <v>0.2032</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.077</v>
+        <v>2.6311</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1918</v>
+        <v>0.411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1147</v>
+        <v>2.2201</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2307</v>
+        <v>-3.8786</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0648</v>
+        <v>-1.8617</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1659</v>
+        <v>-2.0169</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.9576</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4505</v>
+        <v>-0.6465</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7607</v>
+        <v>-0.2764</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3102</v>
+        <v>-0.3701</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.8767</v>
+        <v>-5.6287</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1505</v>
+        <v>-4.552</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.7262</v>
+        <v>-1.0767</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2475</v>
+        <v>-4.1322</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4507</v>
+        <v>-1.7002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2032</v>
+        <v>-2.432</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6311</v>
+        <v>-2.8125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.411</v>
+        <v>-1.3989</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2201</v>
+        <v>-1.4136</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8786</v>
+        <v>-1.3197</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8617</v>
+        <v>-0.3013</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0169</v>
+        <v>-1.0184</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.6101</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4541</v>
+        <v>0.0484</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0839</v>
+        <v>0.2403</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3701</v>
+        <v>-0.192</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.2936</v>
+        <v>-6.3106</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.2478</v>
+        <v>-1.8265</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0459</v>
+        <v>-4.4841</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.1322</v>
+        <v>-4.3077</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7002</v>
+        <v>-2.2566</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.432</v>
+        <v>-2.0511</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.8125</v>
+        <v>-1.077</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3989</v>
+        <v>-1.1918</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4136</v>
+        <v>0.1147</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3197</v>
+        <v>-3.2307</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3013</v>
+        <v>-1.0648</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0184</v>
+        <v>-2.1659</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7401</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6166</v>
+        <v>-0.0454</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4554</v>
+        <v>0.2956</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1612</v>
+        <v>-0.341</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.328900000000001</v>
+        <v>-7.7641</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9177</v>
+        <v>-0.4455</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.4111</v>
+        <v>-7.3187</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2278</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2879</v>
+        <v>-0.7231</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5323</v>
+        <v>-0.0601</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.663</v>
       </c>
       <c r="V9" t="n">
         <v>-3.4207</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.473699999999999</v>
+        <v>-8.082599999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5172</v>
+        <v>-3.6382</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9565</v>
+        <v>-4.4444</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8414</v>
+        <v>-4.1817</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.642</v>
+        <v>-2.5792</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1994</v>
+        <v>-1.6025</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5613</v>
+        <v>-1.665</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0037</v>
+        <v>-1.3989</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.565</v>
+        <v>-0.2661</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2801</v>
+        <v>-2.5167</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6458</v>
+        <v>-1.1803</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6344</v>
+        <v>-1.3364</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.9151</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4128</v>
+        <v>-1.1975</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3942</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0186</v>
+        <v>-0.3118</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.13</v>
+        <v>-2.4859</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-2.4859</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.0001</v>
+        <v>-8.894600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2474</v>
+        <v>-4.784</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.7527</v>
+        <v>-4.1106</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1817</v>
+        <v>-3.8414</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5792</v>
+        <v>-0.642</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6025</v>
+        <v>-3.1994</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.665</v>
+        <v>-0.5613</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3989</v>
+        <v>1.0037</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2661</v>
+        <v>-1.565</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5167</v>
+        <v>-3.2801</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1803</v>
+        <v>-1.6458</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3364</v>
+        <v>-1.6344</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2175</v>
+        <v>-3.9151</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.115</v>
+        <v>-0.0081</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4949</v>
+        <v>0.1274</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6201</v>
+        <v>-0.1355</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4859</v>
+        <v>-1.13</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4859</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-49.6957</v>
+        <v>-48.32559999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-21.3622</v>
+        <v>-19.9925</v>
       </c>
       <c r="F12" t="n">
-        <v>-28.3333</v>
+        <v>-28.3332</v>
       </c>
       <c r="G12" t="n">
         <v>-23.8946</v>
@@ -1366,10 +1366,10 @@
         <v>-1.3176</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.2065</v>
+        <v>-3.206499999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8888</v>
+        <v>1.888799999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-22.577</v>
@@ -1390,13 +1390,13 @@
         <v>6.524999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.5125</v>
+        <v>-3.1423</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4211</v>
+        <v>-1.0514</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0911</v>
+        <v>-2.091</v>
       </c>
       <c r="V12" t="n">
         <v>-8.238199999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.8544</v>
+        <v>11.2854</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3334</v>
+        <v>9.7746</v>
       </c>
       <c r="F13" t="n">
-        <v>1.521</v>
+        <v>1.5108</v>
       </c>
       <c r="G13" t="n">
         <v>6.3455</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6595</v>
+        <v>1.0905</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0227</v>
+        <v>0.4639</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6369</v>
+        <v>0.6267</v>
       </c>
       <c r="V13" t="n">
         <v>1.6743</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.327199999999999</v>
+        <v>9.0137</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5722</v>
+        <v>4.6782</v>
       </c>
       <c r="F14" t="n">
-        <v>3.755</v>
+        <v>4.3355</v>
       </c>
       <c r="G14" t="n">
         <v>4.8594</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4233</v>
+        <v>1.1098</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4817</v>
+        <v>0.5876</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0584</v>
+        <v>0.5221</v>
       </c>
       <c r="V14" t="n">
         <v>1.3045</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6677</v>
+        <v>6.3446</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7129</v>
+        <v>3.2717</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9547</v>
+        <v>3.0729</v>
       </c>
       <c r="G15" t="n">
         <v>0.0108</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3426</v>
+        <v>0.3344</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.1142</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3303</v>
+        <v>0.4485</v>
       </c>
       <c r="V15" t="n">
         <v>4.6944</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8267</v>
+        <v>4.7548</v>
       </c>
       <c r="E16" t="n">
         <v>2.2506</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5761</v>
+        <v>2.5042</v>
       </c>
       <c r="G16" t="n">
         <v>1.2063</v>
@@ -1702,13 +1702,13 @@
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0548</v>
+        <v>0.983</v>
       </c>
       <c r="T16" t="n">
         <v>0.1286</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9263</v>
+        <v>0.8544</v>
       </c>
       <c r="V16" t="n">
         <v>0.3904</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0394</v>
+        <v>4.629</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5764</v>
+        <v>3.1351</v>
       </c>
       <c r="F17" t="n">
-        <v>1.463</v>
+        <v>1.4938</v>
       </c>
       <c r="G17" t="n">
         <v>3.1011</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7365</v>
+        <v>-0.1469</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6165</v>
+        <v>-0.0577</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1201</v>
+        <v>-0.0892</v>
       </c>
       <c r="V17" t="n">
         <v>0.3698</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7413</v>
+        <v>4.2693</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7128</v>
+        <v>1.2716</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0285</v>
+        <v>2.9977</v>
       </c>
       <c r="G18" t="n">
         <v>4.2587</v>
@@ -1858,13 +1858,13 @@
         <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3222</v>
+        <v>0.2058</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4313</v>
+        <v>0.4004</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.6681</v>
+        <v>3.5671</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1006</v>
+        <v>1.3212</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5675</v>
+        <v>2.2458</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4501</v>
+        <v>0.4372</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7816</v>
+        <v>0.4348</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6686</v>
+        <v>0.0024</v>
       </c>
       <c r="J19" t="n">
-        <v>1.09</v>
+        <v>0.2309</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4015</v>
+        <v>0.0397</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6885</v>
+        <v>0.1912</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3601</v>
+        <v>0.2063</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3801</v>
+        <v>0.3951</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0199</v>
+        <v>-0.1889</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3479</v>
+        <v>0.0424</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0106</v>
+        <v>-0.0396</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3373</v>
+        <v>0.082</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.4116</v>
+        <v>3.3623</v>
       </c>
       <c r="E20" t="n">
-        <v>1.433</v>
+        <v>1.4301</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9786</v>
+        <v>1.9322</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4372</v>
+        <v>1.4501</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4348</v>
+        <v>0.7816</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0024</v>
+        <v>0.6686</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2309</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0397</v>
+        <v>0.4015</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1912</v>
+        <v>0.6885</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2063</v>
+        <v>0.3601</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3951</v>
+        <v>0.3801</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1889</v>
+        <v>-0.0199</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1131</v>
+        <v>1.0422</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>0.3401</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1852</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.276</v>
+        <v>2.5024</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6167</v>
+        <v>1.0032</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6593</v>
+        <v>1.4991</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.442</v>
+        <v>2.0794</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.8028</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5212</v>
+        <v>1.2766</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2123</v>
+        <v>1.7687</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09760000000000001</v>
+        <v>1.0037</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1147</v>
+        <v>0.765</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6543</v>
+        <v>0.3107</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0184</v>
+        <v>-0.2009</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6359</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8702</v>
+        <v>0.423</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2966</v>
+        <v>0.3221</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5736</v>
+        <v>0.1009</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6597</v>
+        <v>1.3897</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5562</v>
+        <v>-0.0539</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1036</v>
+        <v>1.4435</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0794</v>
+        <v>-0.442</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8028</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2766</v>
+        <v>-0.5212</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7687</v>
+        <v>0.2123</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0037</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.765</v>
+        <v>0.1147</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3107</v>
+        <v>-0.6543</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2009</v>
+        <v>-0.0184</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.6359</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4196</v>
+        <v>0.9839</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.125</v>
+        <v>0.6261</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2947</v>
+        <v>0.3578</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6366000000000001</v>
+        <v>1.2571</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4741</v>
+        <v>2.0329</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8375</v>
+        <v>-0.7758</v>
       </c>
       <c r="G23" t="n">
         <v>1.6467</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5548999999999999</v>
+        <v>0.0655</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.411</v>
+        <v>0.1478</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.144</v>
+        <v>-0.0823</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3252</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.413</v>
+        <v>-1.1895</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0056</v>
+        <v>-1.7821</v>
       </c>
       <c r="F24" t="n">
         <v>0.5926</v>
@@ -2326,10 +2326,10 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3545</v>
+        <v>-0.131</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U24" t="n">
         <v>-0.012</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>49.6957</v>
+        <v>51.1859</v>
       </c>
       <c r="E25" t="n">
-        <v>28.3333</v>
+        <v>28.3332</v>
       </c>
       <c r="F25" t="n">
-        <v>21.3624</v>
+        <v>22.8523</v>
       </c>
       <c r="G25" t="n">
         <v>23.8947</v>
@@ -2404,13 +2404,13 @@
         <v>19.5757</v>
       </c>
       <c r="S25" t="n">
-        <v>4.512300000000001</v>
+        <v>6.002599999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>2.0909</v>
+        <v>2.091</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4213</v>
+        <v>3.9114</v>
       </c>
       <c r="V25" t="n">
         <v>8.238199999999999</v>
